--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_payshop/lang_payshop__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_payshop/lang_payshop__ui__part_0001.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Fashion Union</t>
+          <t>Liên Minh Thời Trang</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Văn Phòng Công Cộng</t>
+          <t>Văn Phòng Công</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Fashion Union</t>
+          <t>Liên Minh Thời Trang</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Hội Viên Hàng Tháng</t>
+          <t>Gói Thành Viên Hàng Tháng</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Aftershocked Shellhorn</t>
+          <t>Vỏ Sừng Dư Chấn</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Oscillated Shellhorn</t>
+          <t>Sừng Vỏ Dao Động</t>
         </is>
       </c>
     </row>
